--- a/data_fund.xlsx
+++ b/data_fund.xlsx
@@ -4,22 +4,23 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="23145" windowHeight="12525"/>
+    <workbookView windowWidth="28800" windowHeight="12525"/>
   </bookViews>
   <sheets>
-    <sheet name="凡二量化选股3号1期" sheetId="13" r:id="rId1"/>
-    <sheet name="睿郡财富11号1期" sheetId="12" r:id="rId2"/>
-    <sheet name="红筹长线3号" sheetId="9" r:id="rId3"/>
-    <sheet name="宽德" sheetId="11" r:id="rId4"/>
-    <sheet name="辰元" sheetId="8" r:id="rId5"/>
-    <sheet name="安信" sheetId="10" r:id="rId6"/>
-    <sheet name="东方路" sheetId="6" r:id="rId7"/>
-    <sheet name="佳岳" sheetId="5" r:id="rId8"/>
+    <sheet name="聚宽" sheetId="14" r:id="rId1"/>
+    <sheet name="凡二量化选股3号1期" sheetId="13" r:id="rId2"/>
+    <sheet name="睿郡财富11号1期" sheetId="12" r:id="rId3"/>
+    <sheet name="红筹长线3号" sheetId="9" r:id="rId4"/>
+    <sheet name="宽德" sheetId="11" r:id="rId5"/>
+    <sheet name="辰元" sheetId="8" r:id="rId6"/>
+    <sheet name="安信" sheetId="10" r:id="rId7"/>
+    <sheet name="东方路" sheetId="6" r:id="rId8"/>
+    <sheet name="佳岳" sheetId="5" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">红筹长线3号!$A$1:$C$389</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">佳岳!$A$1:$C$108</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">宽德!$A:$C</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">红筹长线3号!$A$1:$C$389</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">佳岳!$A$1:$C$108</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">宽德!$A:$C</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="521">
   <si>
     <t>日期</t>
   </si>
@@ -1608,7 +1609,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="7">
+  <numFmts count="9">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
@@ -1616,8 +1617,10 @@
     <numFmt numFmtId="176" formatCode="0.00000"/>
     <numFmt numFmtId="177" formatCode="0.0000_);[Red]\(0.0000\)"/>
     <numFmt numFmtId="178" formatCode="[$-409]yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="179" formatCode="yyyy/m/d;@"/>
+    <numFmt numFmtId="180" formatCode="0.000_);[Red]\(0.000\)"/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1681,13 +1684,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -2183,13 +2179,16 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2198,125 +2197,122 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2420,16 +2416,13 @@
     <xf numFmtId="177" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2751,6 +2744,748 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr codeName="Sheet7"/>
+  <dimension ref="A1:C66"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
+  <cols>
+    <col min="1" max="1" width="11" style="36"/>
+    <col min="2" max="3" width="12.625" style="37"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="37" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="36">
+        <v>45114</v>
+      </c>
+      <c r="B2" s="37">
+        <v>1</v>
+      </c>
+      <c r="C2" s="37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="36">
+        <v>45121</v>
+      </c>
+      <c r="B3" s="37">
+        <v>1.00780193093368</v>
+      </c>
+      <c r="C3" s="37">
+        <v>1.00780193093368</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="36">
+        <v>45128</v>
+      </c>
+      <c r="B4" s="37">
+        <v>1.01105220834921</v>
+      </c>
+      <c r="C4" s="37">
+        <v>1.01105220834921</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="36">
+        <v>45135</v>
+      </c>
+      <c r="B5" s="37">
+        <v>1.01203961796084</v>
+      </c>
+      <c r="C5" s="37">
+        <v>1.01203961796084</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="36">
+        <v>45142</v>
+      </c>
+      <c r="B6" s="37">
+        <v>1.01533711634373</v>
+      </c>
+      <c r="C6" s="37">
+        <v>1.01533711634373</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="36">
+        <v>45149</v>
+      </c>
+      <c r="B7" s="37">
+        <v>1.01948261594586</v>
+      </c>
+      <c r="C7" s="37">
+        <v>1.01948261594586</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="36">
+        <v>45156</v>
+      </c>
+      <c r="B8" s="37">
+        <v>1.02122005448703</v>
+      </c>
+      <c r="C8" s="37">
+        <v>1.02122005448703</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="36">
+        <v>45163</v>
+      </c>
+      <c r="B9" s="37">
+        <v>1.02312695145077</v>
+      </c>
+      <c r="C9" s="37">
+        <v>1.02312695145077</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="36">
+        <v>45170</v>
+      </c>
+      <c r="B10" s="37">
+        <v>1.02293267070124</v>
+      </c>
+      <c r="C10" s="37">
+        <v>1.02293267070124</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="36">
+        <v>45177</v>
+      </c>
+      <c r="B11" s="37">
+        <v>1.02343283136207</v>
+      </c>
+      <c r="C11" s="37">
+        <v>1.02343283136207</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="36">
+        <v>45184</v>
+      </c>
+      <c r="B12" s="37">
+        <v>1.02859274280723</v>
+      </c>
+      <c r="C12" s="37">
+        <v>1.02859274280723</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="36">
+        <v>45191</v>
+      </c>
+      <c r="B13" s="37">
+        <v>1.02944290254562</v>
+      </c>
+      <c r="C13" s="37">
+        <v>1.02944290254562</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="36">
+        <v>45197</v>
+      </c>
+      <c r="B14" s="37">
+        <v>1.03061972211424</v>
+      </c>
+      <c r="C14" s="37">
+        <v>1.03061972211424</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="36">
+        <v>45212</v>
+      </c>
+      <c r="B15" s="37">
+        <v>1.03220371377229</v>
+      </c>
+      <c r="C15" s="37">
+        <v>1.03220371377229</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="36">
+        <v>45219</v>
+      </c>
+      <c r="B16" s="37">
+        <v>1.03535322845444</v>
+      </c>
+      <c r="C16" s="37">
+        <v>1.03535322845444</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="36">
+        <v>45226</v>
+      </c>
+      <c r="B17" s="37">
+        <v>1.03398584222895</v>
+      </c>
+      <c r="C17" s="37">
+        <v>1.03398584222895</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="36">
+        <v>45233</v>
+      </c>
+      <c r="B18" s="37">
+        <v>1.03504236106639</v>
+      </c>
+      <c r="C18" s="37">
+        <v>1.03504236106639</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="36">
+        <v>45240</v>
+      </c>
+      <c r="B19" s="37">
+        <v>1.03662566764171</v>
+      </c>
+      <c r="C19" s="37">
+        <v>1.03662566764171</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="36">
+        <v>45247</v>
+      </c>
+      <c r="B20" s="37">
+        <v>1.03795163222139</v>
+      </c>
+      <c r="C20" s="37">
+        <v>1.03795163222139</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="36">
+        <v>45254</v>
+      </c>
+      <c r="B21" s="37">
+        <v>1.03961045025336</v>
+      </c>
+      <c r="C21" s="37">
+        <v>1.03961045025336</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="36">
+        <v>45261</v>
+      </c>
+      <c r="B22" s="37">
+        <v>1.03977156556998</v>
+      </c>
+      <c r="C22" s="37">
+        <v>1.03977156556998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="36">
+        <v>45268</v>
+      </c>
+      <c r="B23" s="37">
+        <v>1.0391707726126</v>
+      </c>
+      <c r="C23" s="37">
+        <v>1.0391707726126</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="36">
+        <v>45275</v>
+      </c>
+      <c r="B24" s="37">
+        <v>1.04181314198012</v>
+      </c>
+      <c r="C24" s="37">
+        <v>1.04181314198012</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="36">
+        <v>45282</v>
+      </c>
+      <c r="B25" s="37">
+        <v>1.0443440567838</v>
+      </c>
+      <c r="C25" s="37">
+        <v>1.0443440567838</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="36">
+        <v>45289</v>
+      </c>
+      <c r="B26" s="37">
+        <v>1.04411901009998</v>
+      </c>
+      <c r="C26" s="37">
+        <v>1.04411901009998</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="36">
+        <v>45296</v>
+      </c>
+      <c r="B27" s="37">
+        <v>1.04412511266956</v>
+      </c>
+      <c r="C27" s="37">
+        <v>1.04412511266956</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="36">
+        <v>45303</v>
+      </c>
+      <c r="B28" s="37">
+        <v>1.04464418813183</v>
+      </c>
+      <c r="C28" s="37">
+        <v>1.04464418813183</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="36">
+        <v>45310</v>
+      </c>
+      <c r="B29" s="37">
+        <v>1.04707783795858</v>
+      </c>
+      <c r="C29" s="37">
+        <v>1.04707783795858</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="36">
+        <v>45317</v>
+      </c>
+      <c r="B30" s="37">
+        <v>1.05201273899615</v>
+      </c>
+      <c r="C30" s="37">
+        <v>1.05201273899615</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="36">
+        <v>45324</v>
+      </c>
+      <c r="B31" s="37">
+        <v>1.05349996944583</v>
+      </c>
+      <c r="C31" s="37">
+        <v>1.05349996944583</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="36">
+        <v>45330</v>
+      </c>
+      <c r="B32" s="37">
+        <v>1.06593862411588</v>
+      </c>
+      <c r="C32" s="37">
+        <v>1.06593862411588</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="36">
+        <v>45345</v>
+      </c>
+      <c r="B33" s="37">
+        <v>1.06837227394263</v>
+      </c>
+      <c r="C33" s="37">
+        <v>1.06837227394263</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="36">
+        <v>45352</v>
+      </c>
+      <c r="B34" s="37">
+        <v>1.08202775352605</v>
+      </c>
+      <c r="C34" s="37">
+        <v>1.08202775352605</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="36">
+        <v>45359</v>
+      </c>
+      <c r="B35" s="37">
+        <v>1.08337978120758</v>
+      </c>
+      <c r="C35" s="37">
+        <v>1.08337978120758</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="36">
+        <v>45366</v>
+      </c>
+      <c r="B36" s="37">
+        <v>1.08858508778146</v>
+      </c>
+      <c r="C36" s="37">
+        <v>1.08858508778146</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="36">
+        <v>45373</v>
+      </c>
+      <c r="B37" s="37">
+        <v>1.08912589885407</v>
+      </c>
+      <c r="C37" s="37">
+        <v>1.08912589885407</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="36">
+        <v>45380</v>
+      </c>
+      <c r="B38" s="37">
+        <v>1.08682745179547</v>
+      </c>
+      <c r="C38" s="37">
+        <v>1.08682745179547</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="36">
+        <v>45385</v>
+      </c>
+      <c r="B39" s="37">
+        <v>1.08757106702031</v>
+      </c>
+      <c r="C39" s="37">
+        <v>1.08757106702031</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="36">
+        <v>45394</v>
+      </c>
+      <c r="B40" s="37">
+        <v>1.08723306009993</v>
+      </c>
+      <c r="C40" s="37">
+        <v>1.08723306009993</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="36">
+        <v>45401</v>
+      </c>
+      <c r="B41" s="37">
+        <v>1.09379039435534</v>
+      </c>
+      <c r="C41" s="37">
+        <v>1.09379039435534</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="36">
+        <v>45408</v>
+      </c>
+      <c r="B42" s="37">
+        <v>1.09264117082604</v>
+      </c>
+      <c r="C42" s="37">
+        <v>1.09264117082604</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="36">
+        <v>45412</v>
+      </c>
+      <c r="B43" s="37">
+        <v>1.0930467791305</v>
+      </c>
+      <c r="C43" s="37">
+        <v>1.0930467791305</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="36">
+        <v>45422</v>
+      </c>
+      <c r="B44" s="37">
+        <v>1.09243836667381</v>
+      </c>
+      <c r="C44" s="37">
+        <v>1.09243836667381</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="36">
+        <v>45429</v>
+      </c>
+      <c r="B45" s="37">
+        <v>1.09460161096425</v>
+      </c>
+      <c r="C45" s="37">
+        <v>1.09460161096425</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="36">
+        <v>45436</v>
+      </c>
+      <c r="B46" s="37">
+        <v>1.09791407878399</v>
+      </c>
+      <c r="C46" s="37">
+        <v>1.09791407878399</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="36">
+        <v>45443</v>
+      </c>
+      <c r="B47" s="37">
+        <v>1.09926610646552</v>
+      </c>
+      <c r="C47" s="37">
+        <v>1.09926610646552</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="36">
+        <v>45450</v>
+      </c>
+      <c r="B48" s="37">
+        <v>1.10088853968335</v>
+      </c>
+      <c r="C48" s="37">
+        <v>1.10088853968335</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="36">
+        <v>45457</v>
+      </c>
+      <c r="B49" s="37">
+        <v>1.09838728847253</v>
+      </c>
+      <c r="C49" s="37">
+        <v>1.09838728847253</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="36">
+        <v>45464</v>
+      </c>
+      <c r="B50" s="37">
+        <v>1.10129414798781</v>
+      </c>
+      <c r="C50" s="37">
+        <v>1.10129414798781</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="36">
+        <v>45471</v>
+      </c>
+      <c r="B51" s="37">
+        <v>1.10169975629227</v>
+      </c>
+      <c r="C51" s="37">
+        <v>1.10169975629227</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="36">
+        <v>45478</v>
+      </c>
+      <c r="B52" s="37">
+        <v>1.0958860372617</v>
+      </c>
+      <c r="C52" s="37">
+        <v>1.0958860372617</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" s="36">
+        <v>45485</v>
+      </c>
+      <c r="B53" s="37">
+        <v>1.09548042895725</v>
+      </c>
+      <c r="C53" s="37">
+        <v>1.09548042895725</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" s="36">
+        <v>45492</v>
+      </c>
+      <c r="B54" s="37">
+        <v>1.09656205110247</v>
+      </c>
+      <c r="C54" s="37">
+        <v>1.09656205110247</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" s="36">
+        <v>45499</v>
+      </c>
+      <c r="B55" s="37">
+        <v>1.09690005802285</v>
+      </c>
+      <c r="C55" s="37">
+        <v>1.09690005802285</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" s="36">
+        <v>45506</v>
+      </c>
+      <c r="B56" s="37">
+        <v>1.09980691753813</v>
+      </c>
+      <c r="C56" s="37">
+        <v>1.09980691753813</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" s="36">
+        <v>45513</v>
+      </c>
+      <c r="B57" s="37">
+        <v>1.09798168016807</v>
+      </c>
+      <c r="C57" s="37">
+        <v>1.09798168016807</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" s="36">
+        <v>45520</v>
+      </c>
+      <c r="B58" s="37">
+        <v>1.09683245663877</v>
+      </c>
+      <c r="C58" s="37">
+        <v>1.09683245663877</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" s="36">
+        <v>45527</v>
+      </c>
+      <c r="B59" s="37">
+        <v>1.09642684833432</v>
+      </c>
+      <c r="C59" s="37">
+        <v>1.09642684833432</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" s="36">
+        <v>45534</v>
+      </c>
+      <c r="B60" s="37">
+        <v>1.09723806494323</v>
+      </c>
+      <c r="C60" s="37">
+        <v>1.09723806494323</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" s="36">
+        <v>45541</v>
+      </c>
+      <c r="B61" s="37">
+        <v>1.09392559712349</v>
+      </c>
+      <c r="C61" s="37">
+        <v>1.09392559712349</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" s="36">
+        <v>45548</v>
+      </c>
+      <c r="B62" s="37">
+        <v>1.09216796113751</v>
+      </c>
+      <c r="C62" s="37">
+        <v>1.09216796113751</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" s="36">
+        <v>45555</v>
+      </c>
+      <c r="B63" s="37">
+        <v>1.09439880681202</v>
+      </c>
+      <c r="C63" s="37">
+        <v>1.09439880681202</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" s="36">
+        <v>45562</v>
+      </c>
+      <c r="B64" s="37">
+        <v>1.11413841096232</v>
+      </c>
+      <c r="C64" s="37">
+        <v>1.11413841096232</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" s="36">
+        <v>45565</v>
+      </c>
+      <c r="B65" s="37">
+        <v>1.11589604694831</v>
+      </c>
+      <c r="C65" s="37">
+        <v>1.11589604694831</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" s="36">
+        <v>45574</v>
+      </c>
+      <c r="B66" s="37">
+        <v>1.15584846493743</v>
+      </c>
+      <c r="C66" s="37">
+        <v>1.15584846493743</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:C143"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
@@ -2761,18 +3496,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="37" t="s">
+      <c r="B1" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="38" t="s">
+      <c r="C1" s="35" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="33" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="33">
@@ -2783,7 +3518,7 @@
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="33" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="34">
@@ -2794,7 +3529,7 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="33" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="34">
@@ -2805,7 +3540,7 @@
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="36" t="s">
+      <c r="A5" s="33" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="33">
@@ -2816,7 +3551,7 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="36" t="s">
+      <c r="A6" s="33" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="34">
@@ -2827,7 +3562,7 @@
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="36" t="s">
+      <c r="A7" s="33" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="33">
@@ -2838,7 +3573,7 @@
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="36" t="s">
+      <c r="A8" s="33" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="33">
@@ -2849,7 +3584,7 @@
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="36" t="s">
+      <c r="A9" s="33" t="s">
         <v>10</v>
       </c>
       <c r="B9" s="33">
@@ -2860,7 +3595,7 @@
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="36" t="s">
+      <c r="A10" s="33" t="s">
         <v>11</v>
       </c>
       <c r="B10" s="33">
@@ -2871,7 +3606,7 @@
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="36" t="s">
+      <c r="A11" s="33" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="33">
@@ -2882,7 +3617,7 @@
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="36" t="s">
+      <c r="A12" s="33" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="33">
@@ -2893,7 +3628,7 @@
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="36" t="s">
+      <c r="A13" s="33" t="s">
         <v>14</v>
       </c>
       <c r="B13" s="33">
@@ -2904,7 +3639,7 @@
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="36" t="s">
+      <c r="A14" s="33" t="s">
         <v>15</v>
       </c>
       <c r="B14" s="33">
@@ -2915,7 +3650,7 @@
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="36" t="s">
+      <c r="A15" s="33" t="s">
         <v>16</v>
       </c>
       <c r="B15" s="33">
@@ -2926,7 +3661,7 @@
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="36" t="s">
+      <c r="A16" s="33" t="s">
         <v>17</v>
       </c>
       <c r="B16" s="33">
@@ -2937,7 +3672,7 @@
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="36" t="s">
+      <c r="A17" s="33" t="s">
         <v>18</v>
       </c>
       <c r="B17" s="33">
@@ -2948,7 +3683,7 @@
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="36" t="s">
+      <c r="A18" s="33" t="s">
         <v>19</v>
       </c>
       <c r="B18" s="33">
@@ -2959,7 +3694,7 @@
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="36" t="s">
+      <c r="A19" s="33" t="s">
         <v>20</v>
       </c>
       <c r="B19" s="33">
@@ -2970,7 +3705,7 @@
       </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="36" t="s">
+      <c r="A20" s="33" t="s">
         <v>21</v>
       </c>
       <c r="B20" s="33">
@@ -2981,7 +3716,7 @@
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="36" t="s">
+      <c r="A21" s="33" t="s">
         <v>22</v>
       </c>
       <c r="B21" s="33">
@@ -2992,7 +3727,7 @@
       </c>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="36" t="s">
+      <c r="A22" s="33" t="s">
         <v>23</v>
       </c>
       <c r="B22" s="33">
@@ -3003,7 +3738,7 @@
       </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="36" t="s">
+      <c r="A23" s="33" t="s">
         <v>24</v>
       </c>
       <c r="B23" s="33">
@@ -3014,7 +3749,7 @@
       </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="36" t="s">
+      <c r="A24" s="33" t="s">
         <v>25</v>
       </c>
       <c r="B24" s="33">
@@ -3025,7 +3760,7 @@
       </c>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="36" t="s">
+      <c r="A25" s="33" t="s">
         <v>26</v>
       </c>
       <c r="B25" s="33">
@@ -3036,7 +3771,7 @@
       </c>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="36" t="s">
+      <c r="A26" s="33" t="s">
         <v>27</v>
       </c>
       <c r="B26" s="33">
@@ -3047,7 +3782,7 @@
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="36" t="s">
+      <c r="A27" s="33" t="s">
         <v>28</v>
       </c>
       <c r="B27" s="33">
@@ -3058,7 +3793,7 @@
       </c>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="36" t="s">
+      <c r="A28" s="33" t="s">
         <v>29</v>
       </c>
       <c r="B28" s="33">
@@ -3069,7 +3804,7 @@
       </c>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="36" t="s">
+      <c r="A29" s="33" t="s">
         <v>30</v>
       </c>
       <c r="B29" s="33">
@@ -3080,7 +3815,7 @@
       </c>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="36" t="s">
+      <c r="A30" s="33" t="s">
         <v>31</v>
       </c>
       <c r="B30" s="33">
@@ -3091,7 +3826,7 @@
       </c>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="36" t="s">
+      <c r="A31" s="33" t="s">
         <v>32</v>
       </c>
       <c r="B31" s="33">
@@ -3102,7 +3837,7 @@
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="36" t="s">
+      <c r="A32" s="33" t="s">
         <v>33</v>
       </c>
       <c r="B32" s="33">
@@ -3113,7 +3848,7 @@
       </c>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="36" t="s">
+      <c r="A33" s="33" t="s">
         <v>34</v>
       </c>
       <c r="B33" s="33">
@@ -3124,7 +3859,7 @@
       </c>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="36" t="s">
+      <c r="A34" s="33" t="s">
         <v>35</v>
       </c>
       <c r="B34" s="33">
@@ -3135,7 +3870,7 @@
       </c>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="36" t="s">
+      <c r="A35" s="33" t="s">
         <v>36</v>
       </c>
       <c r="B35" s="33">
@@ -3146,7 +3881,7 @@
       </c>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" s="36" t="s">
+      <c r="A36" s="33" t="s">
         <v>37</v>
       </c>
       <c r="B36" s="33">
@@ -3157,7 +3892,7 @@
       </c>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37" s="36" t="s">
+      <c r="A37" s="33" t="s">
         <v>38</v>
       </c>
       <c r="B37" s="33">
@@ -3168,7 +3903,7 @@
       </c>
     </row>
     <row r="38" spans="1:3">
-      <c r="A38" s="36" t="s">
+      <c r="A38" s="33" t="s">
         <v>39</v>
       </c>
       <c r="B38" s="33">
@@ -3179,7 +3914,7 @@
       </c>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="36" t="s">
+      <c r="A39" s="33" t="s">
         <v>40</v>
       </c>
       <c r="B39" s="33">
@@ -3190,7 +3925,7 @@
       </c>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="36" t="s">
+      <c r="A40" s="33" t="s">
         <v>41</v>
       </c>
       <c r="B40" s="33">
@@ -3201,7 +3936,7 @@
       </c>
     </row>
     <row r="41" spans="1:3">
-      <c r="A41" s="36" t="s">
+      <c r="A41" s="33" t="s">
         <v>42</v>
       </c>
       <c r="B41" s="33">
@@ -3212,7 +3947,7 @@
       </c>
     </row>
     <row r="42" spans="1:3">
-      <c r="A42" s="36" t="s">
+      <c r="A42" s="33" t="s">
         <v>43</v>
       </c>
       <c r="B42" s="33">
@@ -3223,7 +3958,7 @@
       </c>
     </row>
     <row r="43" spans="1:3">
-      <c r="A43" s="36" t="s">
+      <c r="A43" s="33" t="s">
         <v>44</v>
       </c>
       <c r="B43" s="33">
@@ -3234,7 +3969,7 @@
       </c>
     </row>
     <row r="44" spans="1:3">
-      <c r="A44" s="36" t="s">
+      <c r="A44" s="33" t="s">
         <v>45</v>
       </c>
       <c r="B44" s="33">
@@ -3245,7 +3980,7 @@
       </c>
     </row>
     <row r="45" spans="1:3">
-      <c r="A45" s="36" t="s">
+      <c r="A45" s="33" t="s">
         <v>46</v>
       </c>
       <c r="B45" s="33">
@@ -3256,7 +3991,7 @@
       </c>
     </row>
     <row r="46" spans="1:3">
-      <c r="A46" s="36" t="s">
+      <c r="A46" s="33" t="s">
         <v>47</v>
       </c>
       <c r="B46" s="33">
@@ -3267,7 +4002,7 @@
       </c>
     </row>
     <row r="47" spans="1:3">
-      <c r="A47" s="36" t="s">
+      <c r="A47" s="33" t="s">
         <v>48</v>
       </c>
       <c r="B47" s="33">
@@ -3278,7 +4013,7 @@
       </c>
     </row>
     <row r="48" spans="1:3">
-      <c r="A48" s="36" t="s">
+      <c r="A48" s="33" t="s">
         <v>49</v>
       </c>
       <c r="B48" s="33">
@@ -3289,7 +4024,7 @@
       </c>
     </row>
     <row r="49" spans="1:3">
-      <c r="A49" s="36" t="s">
+      <c r="A49" s="33" t="s">
         <v>50</v>
       </c>
       <c r="B49" s="33">
@@ -3300,7 +4035,7 @@
       </c>
     </row>
     <row r="50" spans="1:3">
-      <c r="A50" s="36" t="s">
+      <c r="A50" s="33" t="s">
         <v>51</v>
       </c>
       <c r="B50" s="33">
@@ -3311,7 +4046,7 @@
       </c>
     </row>
     <row r="51" spans="1:3">
-      <c r="A51" s="36" t="s">
+      <c r="A51" s="33" t="s">
         <v>52</v>
       </c>
       <c r="B51" s="33">
@@ -3322,7 +4057,7 @@
       </c>
     </row>
     <row r="52" spans="1:3">
-      <c r="A52" s="36" t="s">
+      <c r="A52" s="33" t="s">
         <v>53</v>
       </c>
       <c r="B52" s="33">
@@ -3333,7 +4068,7 @@
       </c>
     </row>
     <row r="53" spans="1:3">
-      <c r="A53" s="36" t="s">
+      <c r="A53" s="33" t="s">
         <v>54</v>
       </c>
       <c r="B53" s="33">
@@ -3344,7 +4079,7 @@
       </c>
     </row>
     <row r="54" spans="1:3">
-      <c r="A54" s="36" t="s">
+      <c r="A54" s="33" t="s">
         <v>55</v>
       </c>
       <c r="B54" s="33">
@@ -3355,7 +4090,7 @@
       </c>
     </row>
     <row r="55" spans="1:3">
-      <c r="A55" s="36" t="s">
+      <c r="A55" s="33" t="s">
         <v>56</v>
       </c>
       <c r="B55" s="33">
@@ -3366,7 +4101,7 @@
       </c>
     </row>
     <row r="56" spans="1:3">
-      <c r="A56" s="36" t="s">
+      <c r="A56" s="33" t="s">
         <v>57</v>
       </c>
       <c r="B56" s="33">
@@ -3377,7 +4112,7 @@
       </c>
     </row>
     <row r="57" spans="1:3">
-      <c r="A57" s="36" t="s">
+      <c r="A57" s="33" t="s">
         <v>58</v>
       </c>
       <c r="B57" s="33">
@@ -3388,7 +4123,7 @@
       </c>
     </row>
     <row r="58" spans="1:3">
-      <c r="A58" s="36" t="s">
+      <c r="A58" s="33" t="s">
         <v>59</v>
       </c>
       <c r="B58" s="33">
@@ -3399,7 +4134,7 @@
       </c>
     </row>
     <row r="59" spans="1:3">
-      <c r="A59" s="36" t="s">
+      <c r="A59" s="33" t="s">
         <v>60</v>
       </c>
       <c r="B59" s="33">
@@ -3410,7 +4145,7 @@
       </c>
     </row>
     <row r="60" spans="1:3">
-      <c r="A60" s="36" t="s">
+      <c r="A60" s="33" t="s">
         <v>61</v>
       </c>
       <c r="B60" s="33">
@@ -3421,7 +4156,7 @@
       </c>
     </row>
     <row r="61" spans="1:3">
-      <c r="A61" s="36" t="s">
+      <c r="A61" s="33" t="s">
         <v>62</v>
       </c>
       <c r="B61" s="33">
@@ -3432,7 +4167,7 @@
       </c>
     </row>
     <row r="62" spans="1:3">
-      <c r="A62" s="36" t="s">
+      <c r="A62" s="33" t="s">
         <v>63</v>
       </c>
       <c r="B62" s="33">
@@ -3443,7 +4178,7 @@
       </c>
     </row>
     <row r="63" spans="1:3">
-      <c r="A63" s="36" t="s">
+      <c r="A63" s="33" t="s">
         <v>64</v>
       </c>
       <c r="B63" s="33">
@@ -3454,7 +4189,7 @@
       </c>
     </row>
     <row r="64" spans="1:3">
-      <c r="A64" s="36" t="s">
+      <c r="A64" s="33" t="s">
         <v>65</v>
       </c>
       <c r="B64" s="33">
@@ -3465,7 +4200,7 @@
       </c>
     </row>
     <row r="65" spans="1:3">
-      <c r="A65" s="36" t="s">
+      <c r="A65" s="33" t="s">
         <v>66</v>
       </c>
       <c r="B65" s="33">
@@ -3476,7 +4211,7 @@
       </c>
     </row>
     <row r="66" spans="1:3">
-      <c r="A66" s="36" t="s">
+      <c r="A66" s="33" t="s">
         <v>67</v>
       </c>
       <c r="B66" s="33">
@@ -3487,7 +4222,7 @@
       </c>
     </row>
     <row r="67" spans="1:3">
-      <c r="A67" s="36" t="s">
+      <c r="A67" s="33" t="s">
         <v>68</v>
       </c>
       <c r="B67" s="33">
@@ -3498,7 +4233,7 @@
       </c>
     </row>
     <row r="68" spans="1:3">
-      <c r="A68" s="36" t="s">
+      <c r="A68" s="33" t="s">
         <v>69</v>
       </c>
       <c r="B68" s="33">
@@ -3509,7 +4244,7 @@
       </c>
     </row>
     <row r="69" spans="1:3">
-      <c r="A69" s="36" t="s">
+      <c r="A69" s="33" t="s">
         <v>70</v>
       </c>
       <c r="B69" s="33">
@@ -3520,7 +4255,7 @@
       </c>
     </row>
     <row r="70" spans="1:3">
-      <c r="A70" s="36" t="s">
+      <c r="A70" s="33" t="s">
         <v>71</v>
       </c>
       <c r="B70" s="33">
@@ -3531,7 +4266,7 @@
       </c>
     </row>
     <row r="71" spans="1:3">
-      <c r="A71" s="36" t="s">
+      <c r="A71" s="33" t="s">
         <v>72</v>
       </c>
       <c r="B71" s="33">
@@ -3542,7 +4277,7 @@
       </c>
     </row>
     <row r="72" spans="1:3">
-      <c r="A72" s="36" t="s">
+      <c r="A72" s="33" t="s">
         <v>73</v>
       </c>
       <c r="B72" s="33">
@@ -3553,7 +4288,7 @@
       </c>
     </row>
     <row r="73" spans="1:3">
-      <c r="A73" s="36" t="s">
+      <c r="A73" s="33" t="s">
         <v>74</v>
       </c>
       <c r="B73" s="33">
@@ -3564,7 +4299,7 @@
       </c>
     </row>
     <row r="74" spans="1:3">
-      <c r="A74" s="36" t="s">
+      <c r="A74" s="33" t="s">
         <v>75</v>
       </c>
       <c r="B74" s="33">
@@ -3575,7 +4310,7 @@
       </c>
     </row>
     <row r="75" spans="1:3">
-      <c r="A75" s="36" t="s">
+      <c r="A75" s="33" t="s">
         <v>76</v>
       </c>
       <c r="B75" s="33">
@@ -3586,7 +4321,7 @@
       </c>
     </row>
     <row r="76" spans="1:3">
-      <c r="A76" s="36" t="s">
+      <c r="A76" s="33" t="s">
         <v>77</v>
       </c>
       <c r="B76" s="33">
@@ -3597,7 +4332,7 @@
       </c>
     </row>
     <row r="77" spans="1:3">
-      <c r="A77" s="36" t="s">
+      <c r="A77" s="33" t="s">
         <v>78</v>
       </c>
       <c r="B77" s="33">
@@ -3608,7 +4343,7 @@
       </c>
     </row>
     <row r="78" spans="1:3">
-      <c r="A78" s="36" t="s">
+      <c r="A78" s="33" t="s">
         <v>79</v>
       </c>
       <c r="B78" s="33">
@@ -3619,7 +4354,7 @@
       </c>
     </row>
     <row r="79" spans="1:3">
-      <c r="A79" s="36" t="s">
+      <c r="A79" s="33" t="s">
         <v>80</v>
       </c>
       <c r="B79" s="33">
@@ -3630,7 +4365,7 @@
       </c>
     </row>
     <row r="80" spans="1:3">
-      <c r="A80" s="36" t="s">
+      <c r="A80" s="33" t="s">
         <v>81</v>
       </c>
       <c r="B80" s="33">
@@ -3641,7 +4376,7 @@
       </c>
     </row>
     <row r="81" spans="1:3">
-      <c r="A81" s="36" t="s">
+      <c r="A81" s="33" t="s">
         <v>82</v>
       </c>
       <c r="B81" s="33">
@@ -3652,7 +4387,7 @@
       </c>
     </row>
     <row r="82" spans="1:3">
-      <c r="A82" s="36" t="s">
+      <c r="A82" s="33" t="s">
         <v>83</v>
       </c>
       <c r="B82" s="33">
@@ -3663,7 +4398,7 @@
       </c>
     </row>
     <row r="83" spans="1:3">
-      <c r="A83" s="36" t="s">
+      <c r="A83" s="33" t="s">
         <v>84</v>
       </c>
       <c r="B83" s="33">
@@ -3674,7 +4409,7 @@
       </c>
     </row>
     <row r="84" spans="1:3">
-      <c r="A84" s="36" t="s">
+      <c r="A84" s="33" t="s">
         <v>85</v>
       </c>
       <c r="B84" s="33">
@@ -3685,7 +4420,7 @@
       </c>
     </row>
     <row r="85" spans="1:3">
-      <c r="A85" s="36" t="s">
+      <c r="A85" s="33" t="s">
         <v>86</v>
       </c>
       <c r="B85" s="33">
@@ -3696,7 +4431,7 @@
       </c>
     </row>
     <row r="86" spans="1:3">
-      <c r="A86" s="36" t="s">
+      <c r="A86" s="33" t="s">
         <v>87</v>
       </c>
       <c r="B86" s="33">
@@ -3707,7 +4442,7 @@
       </c>
     </row>
     <row r="87" spans="1:3">
-      <c r="A87" s="36" t="s">
+      <c r="A87" s="33" t="s">
         <v>88</v>
       </c>
       <c r="B87" s="33">
@@ -3718,7 +4453,7 @@
       </c>
     </row>
     <row r="88" spans="1:3">
-      <c r="A88" s="36" t="s">
+      <c r="A88" s="33" t="s">
         <v>89</v>
       </c>
       <c r="B88" s="33">
@@ -3729,7 +4464,7 @@
       </c>
     </row>
     <row r="89" spans="1:3">
-      <c r="A89" s="36" t="s">
+      <c r="A89" s="33" t="s">
         <v>90</v>
       </c>
       <c r="B89" s="33">
@@ -3740,7 +4475,7 @@
       </c>
     </row>
     <row r="90" spans="1:3">
-      <c r="A90" s="36" t="s">
+      <c r="A90" s="33" t="s">
         <v>91</v>
       </c>
       <c r="B90" s="33">
@@ -3751,7 +4486,7 @@
       </c>
     </row>
     <row r="91" spans="1:3">
-      <c r="A91" s="36" t="s">
+      <c r="A91" s="33" t="s">
         <v>92</v>
       </c>
       <c r="B91" s="33">
@@ -3762,7 +4497,7 @@
       </c>
     </row>
     <row r="92" spans="1:3">
-      <c r="A92" s="36" t="s">
+      <c r="A92" s="33" t="s">
         <v>93</v>
       </c>
       <c r="B92" s="33">
@@ -3773,7 +4508,7 @@
       </c>
     </row>
     <row r="93" spans="1:3">
-      <c r="A93" s="36" t="s">
+      <c r="A93" s="33" t="s">
         <v>94</v>
       </c>
       <c r="B93" s="33">
@@ -3784,7 +4519,7 @@
       </c>
     </row>
     <row r="94" spans="1:3">
-      <c r="A94" s="36" t="s">
+      <c r="A94" s="33" t="s">
         <v>95</v>
       </c>
       <c r="B94" s="33">
@@ -3795,7 +4530,7 @@
       </c>
     </row>
     <row r="95" spans="1:3">
-      <c r="A95" s="36" t="s">
+      <c r="A95" s="33" t="s">
         <v>96</v>
       </c>
       <c r="B95" s="33">
@@ -3806,7 +4541,7 @@
       </c>
     </row>
     <row r="96" spans="1:3">
-      <c r="A96" s="36" t="s">
+      <c r="A96" s="33" t="s">
         <v>97</v>
       </c>
       <c r="B96" s="33">
@@ -3817,7 +4552,7 @@
       </c>
     </row>
     <row r="97" spans="1:3">
-      <c r="A97" s="36" t="s">
+      <c r="A97" s="33" t="s">
         <v>98</v>
       </c>
       <c r="B97" s="33">
@@ -3828,7 +4563,7 @@
       </c>
     </row>
     <row r="98" spans="1:3">
-      <c r="A98" s="36" t="s">
+      <c r="A98" s="33" t="s">
         <v>99</v>
       </c>
       <c r="B98" s="33">
@@ -3839,7 +4574,7 @@
       </c>
     </row>
     <row r="99" spans="1:3">
-      <c r="A99" s="36" t="s">
+      <c r="A99" s="33" t="s">
         <v>100</v>
       </c>
       <c r="B99" s="33">
@@ -3850,7 +4585,7 @@
       </c>
     </row>
     <row r="100" spans="1:3">
-      <c r="A100" s="36" t="s">
+      <c r="A100" s="33" t="s">
         <v>101</v>
       </c>
       <c r="B100" s="33">
@@ -3861,7 +4596,7 @@
       </c>
     </row>
     <row r="101" spans="1:3">
-      <c r="A101" s="36" t="s">
+      <c r="A101" s="33" t="s">
         <v>102</v>
       </c>
       <c r="B101" s="33">
@@ -3872,7 +4607,7 @@
       </c>
     </row>
     <row r="102" spans="1:3">
-      <c r="A102" s="36" t="s">
+      <c r="A102" s="33" t="s">
         <v>103</v>
       </c>
       <c r="B102" s="33">
@@ -3883,7 +4618,7 @@
       </c>
     </row>
     <row r="103" spans="1:3">
-      <c r="A103" s="36" t="s">
+      <c r="A103" s="33" t="s">
         <v>104</v>
       </c>
       <c r="B103" s="33">
@@ -3894,7 +4629,7 @@
       </c>
     </row>
     <row r="104" spans="1:3">
-      <c r="A104" s="36" t="s">
+      <c r="A104" s="33" t="s">
         <v>105</v>
       </c>
       <c r="B104" s="33">
@@ -3905,7 +4640,7 @@
       </c>
     </row>
     <row r="105" spans="1:3">
-      <c r="A105" s="36" t="s">
+      <c r="A105" s="33" t="s">
         <v>106</v>
       </c>
       <c r="B105" s="33">
@@ -3916,7 +4651,7 @@
       </c>
     </row>
     <row r="106" spans="1:3">
-      <c r="A106" s="36" t="s">
+      <c r="A106" s="33" t="s">
         <v>107</v>
       </c>
       <c r="B106" s="33">
@@ -3927,7 +4662,7 @@
       </c>
     </row>
     <row r="107" spans="1:3">
-      <c r="A107" s="36" t="s">
+      <c r="A107" s="33" t="s">
         <v>108</v>
       </c>
       <c r="B107" s="33">
@@ -3938,7 +4673,7 @@
       </c>
     </row>
     <row r="108" spans="1:3">
-      <c r="A108" s="36" t="s">
+      <c r="A108" s="33" t="s">
         <v>109</v>
       </c>
       <c r="B108" s="33">
@@ -3949,7 +4684,7 @@
       </c>
     </row>
     <row r="109" spans="1:3">
-      <c r="A109" s="36" t="s">
+      <c r="A109" s="33" t="s">
         <v>110</v>
       </c>
       <c r="B109" s="33">
@@ -3960,7 +4695,7 @@
       </c>
     </row>
     <row r="110" spans="1:3">
-      <c r="A110" s="36" t="s">
+      <c r="A110" s="33" t="s">
         <v>111</v>
       </c>
       <c r="B110" s="33">
@@ -3971,7 +4706,7 @@
       </c>
     </row>
     <row r="111" spans="1:3">
-      <c r="A111" s="36" t="s">
+      <c r="A111" s="33" t="s">
         <v>112</v>
       </c>
       <c r="B111" s="33">
@@ -3982,7 +4717,7 @@
       </c>
     </row>
     <row r="112" spans="1:3">
-      <c r="A112" s="36" t="s">
+      <c r="A112" s="33" t="s">
         <v>113</v>
       </c>
       <c r="B112" s="33">
@@ -3993,7 +4728,7 @@
       </c>
     </row>
     <row r="113" spans="1:3">
-      <c r="A113" s="36" t="s">
+      <c r="A113" s="33" t="s">
         <v>114</v>
       </c>
       <c r="B113" s="33">
@@ -4004,7 +4739,7 @@
       </c>
     </row>
     <row r="114" spans="1:3">
-      <c r="A114" s="36" t="s">
+      <c r="A114" s="33" t="s">
         <v>115</v>
       </c>
       <c r="B114" s="33">
@@ -4015,7 +4750,7 @@
       </c>
     </row>
     <row r="115" spans="1:3">
-      <c r="A115" s="36" t="s">
+      <c r="A115" s="33" t="s">
         <v>116</v>
       </c>
       <c r="B115" s="33">
@@ -4026,7 +4761,7 @@
       </c>
     </row>
     <row r="116" spans="1:3">
-      <c r="A116" s="36" t="s">
+      <c r="A116" s="33" t="s">
         <v>117</v>
       </c>
       <c r="B116" s="33">
@@ -4037,7 +4772,7 @@
       </c>
     </row>
     <row r="117" spans="1:3">
-      <c r="A117" s="36" t="s">
+      <c r="A117" s="33" t="s">
         <v>118</v>
       </c>
       <c r="B117" s="33">
@@ -4048,7 +4783,7 @@
       </c>
     </row>
     <row r="118" spans="1:3">
-      <c r="A118" s="36" t="s">
+      <c r="A118" s="33" t="s">
         <v>119</v>
       </c>
       <c r="B118" s="33">
@@ -4059,7 +4794,7 @@
       </c>
     </row>
     <row r="119" spans="1:3">
-      <c r="A119" s="36" t="s">
+      <c r="A119" s="33" t="s">
         <v>120</v>
       </c>
       <c r="B119" s="33">
@@ -4070,7 +4805,7 @@
       </c>
     </row>
     <row r="120" spans="1:3">
-      <c r="A120" s="36" t="s">
+      <c r="A120" s="33" t="s">
         <v>121</v>
       </c>
       <c r="B120" s="33">
@@ -4081,7 +4816,7 @@
       </c>
     </row>
     <row r="121" spans="1:3">
-      <c r="A121" s="36" t="s">
+      <c r="A121" s="33" t="s">
         <v>122</v>
       </c>
       <c r="B121" s="33">
@@ -4092,7 +4827,7 @@
       </c>
     </row>
     <row r="122" spans="1:3">
-      <c r="A122" s="36" t="s">
+      <c r="A122" s="33" t="s">
         <v>123</v>
       </c>
       <c r="B122" s="33">
@@ -4103,7 +4838,7 @@
       </c>
     </row>
     <row r="123" spans="1:3">
-      <c r="A123" s="36" t="s">
+      <c r="A123" s="33" t="s">
         <v>124</v>
       </c>
       <c r="B123" s="33">
@@ -4114,7 +4849,7 @@
       </c>
     </row>
     <row r="124" spans="1:3">
-      <c r="A124" s="36" t="s">
+      <c r="A124" s="33" t="s">
         <v>125</v>
       </c>
       <c r="B124" s="33">
@@ -4125,7 +4860,7 @@
       </c>
     </row>
     <row r="125" spans="1:3">
-      <c r="A125" s="36" t="s">
+      <c r="A125" s="33" t="s">
         <v>126</v>
       </c>
       <c r="B125" s="33">
@@ -4136,7 +4871,7 @@
       </c>
     </row>
     <row r="126" spans="1:3">
-      <c r="A126" s="36" t="s">
+      <c r="A126" s="33" t="s">
         <v>127</v>
       </c>
       <c r="B126" s="33">
@@ -4147,7 +4882,7 @@
       </c>
     </row>
     <row r="127" spans="1:3">
-      <c r="A127" s="36" t="s">
+      <c r="A127" s="33" t="s">
         <v>128</v>
       </c>
       <c r="B127" s="33">
@@ -4158,7 +4893,7 @@
       </c>
     </row>
     <row r="128" spans="1:3">
-      <c r="A128" s="36" t="s">
+      <c r="A128" s="33" t="s">
         <v>129</v>
       </c>
       <c r="B128" s="33">
@@ -4169,7 +4904,7 @@
       </c>
     </row>
     <row r="129" spans="1:3">
-      <c r="A129" s="36" t="s">
+      <c r="A129" s="33" t="s">
         <v>130</v>
       </c>
       <c r="B129" s="33">
@@ -4180,7 +4915,7 @@
       </c>
     </row>
     <row r="130" spans="1:3">
-      <c r="A130" s="36" t="s">
+      <c r="A130" s="33" t="s">
         <v>131</v>
       </c>
       <c r="B130" s="33">
@@ -4191,7 +4926,7 @@
       </c>
     </row>
     <row r="131" spans="1:3">
-      <c r="A131" s="36" t="s">
+      <c r="A131" s="33" t="s">
         <v>132</v>
       </c>
       <c r="B131" s="33">
@@ -4202,7 +4937,7 @@
       </c>
     </row>
     <row r="132" spans="1:3">
-      <c r="A132" s="36" t="s">
+      <c r="A132" s="33" t="s">
         <v>133</v>
       </c>
       <c r="B132" s="33">
@@ -4213,7 +4948,7 @@
       </c>
     </row>
     <row r="133" spans="1:3">
-      <c r="A133" s="36" t="s">
+      <c r="A133" s="33" t="s">
         <v>134</v>
       </c>
       <c r="B133" s="33">
@@ -4224,7 +4959,7 @@
       </c>
     </row>
     <row r="134" spans="1:3">
-      <c r="A134" s="36" t="s">
+      <c r="A134" s="33" t="s">
         <v>135</v>
       </c>
       <c r="B134" s="33">
@@ -4235,7 +4970,7 @@
       </c>
     </row>
     <row r="135" spans="1:3">
-      <c r="A135" s="36" t="s">
+      <c r="A135" s="33" t="s">
         <v>136</v>
       </c>
       <c r="B135" s="33">
@@ -4246,7 +4981,7 @@
       </c>
     </row>
     <row r="136" spans="1:3">
-      <c r="A136" s="36" t="s">
+      <c r="A136" s="33" t="s">
         <v>137</v>
       </c>
       <c r="B136" s="33">
@@ -4257,7 +4992,7 @@
       </c>
     </row>
     <row r="137" spans="1:3">
-      <c r="A137" s="36" t="s">
+      <c r="A137" s="33" t="s">
         <v>138</v>
       </c>
       <c r="B137" s="33">
@@ -4268,7 +5003,7 @@
       </c>
     </row>
     <row r="138" spans="1:3">
-      <c r="A138" s="36" t="s">
+      <c r="A138" s="33" t="s">
         <v>139</v>
       </c>
       <c r="B138" s="33">
@@ -4279,7 +5014,7 @@
       </c>
     </row>
     <row r="139" spans="1:3">
-      <c r="A139" s="36" t="s">
+      <c r="A139" s="33" t="s">
         <v>140</v>
       </c>
       <c r="B139" s="33">
@@ -4290,7 +5025,7 @@
       </c>
     </row>
     <row r="140" spans="1:3">
-      <c r="A140" s="36" t="s">
+      <c r="A140" s="33" t="s">
         <v>141</v>
       </c>
       <c r="B140" s="33">
@@ -4301,7 +5036,7 @@
       </c>
     </row>
     <row r="141" spans="1:3">
-      <c r="A141" s="36" t="s">
+      <c r="A141" s="33" t="s">
         <v>142</v>
       </c>
       <c r="B141" s="33">
@@ -4312,7 +5047,7 @@
       </c>
     </row>
     <row r="142" spans="1:3">
-      <c r="A142" s="36" t="s">
+      <c r="A142" s="33" t="s">
         <v>143</v>
       </c>
       <c r="B142" s="33">
@@ -4323,7 +5058,7 @@
       </c>
     </row>
     <row r="143" spans="1:3">
-      <c r="A143" s="36" t="s">
+      <c r="A143" s="33" t="s">
         <v>144</v>
       </c>
       <c r="B143" s="33">
@@ -4339,7 +5074,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:C171"/>
@@ -6236,7 +6971,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:C389"/>
@@ -10532,7 +11267,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:C126"/>
@@ -11935,7 +12670,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:C357"/>
@@ -15880,7 +16615,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:C404"/>
@@ -20341,7 +21076,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet13"/>
   <dimension ref="A1:C142"/>
@@ -21923,7 +22658,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:C108"/>
